--- a/Task_Tracker.xlsx
+++ b/Task_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Polytechnic\2026\HK Summer 2026\Block2\Du-an-01\credit-risk-classifier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43154ED5-2DC9-4DBD-BE10-DC3C1C65307C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FB8CAB-DA86-45D4-8C62-2D325D7DF25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Overview" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
   <si>
     <t>Rossmann Store Sales - Project Timeline</t>
   </si>
@@ -96,33 +96,12 @@
     <t>T01</t>
   </si>
   <si>
-    <t>G1</t>
-  </si>
-  <si>
-    <t>Ngày 1</t>
-  </si>
-  <si>
-    <t>Trưởng nhóm</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
     <t>T02</t>
   </si>
   <si>
-    <t>Toàn nhóm</t>
-  </si>
-  <si>
     <t>T40</t>
   </si>
   <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>Ngày 18</t>
-  </si>
-  <si>
     <t>Weekly Log - Rossmann Project</t>
   </si>
   <si>
@@ -144,318 +123,120 @@
     <t>Người ghi</t>
   </si>
   <si>
-    <t>Kickoff dự án, giới thiệu yêu cầu &amp; timeline</t>
-  </si>
-  <si>
-    <t>Chia nhóm &amp; chọn dataset Rossmann</t>
-  </si>
-  <si>
     <t>T03</t>
   </si>
   <si>
-    <t>Phân chia vai trò rõ ràng</t>
-  </si>
-  <si>
     <t>T04</t>
   </si>
   <si>
-    <t>Tạo Git Repository + README</t>
-  </si>
-  <si>
     <t>T05</t>
   </si>
   <si>
-    <t>Phân tích cấu trúc dataset (train, store, test)</t>
-  </si>
-  <si>
-    <t>Ngày 2</t>
-  </si>
-  <si>
     <t>T06</t>
   </si>
   <si>
-    <t>Thiết kế schema PostgreSQL</t>
-  </si>
-  <si>
-    <t>Data Engineer</t>
-  </si>
-  <si>
     <t>T07</t>
   </si>
   <si>
-    <t>Vẽ ERD (Entity Relationship Diagram)</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>T08</t>
   </si>
   <si>
-    <t>Import dữ liệu vào PostgreSQL</t>
-  </si>
-  <si>
-    <t>Ngày 3</t>
-  </si>
-  <si>
     <t>T09</t>
   </si>
   <si>
-    <t>Kiểm tra datatype &amp; encoding</t>
-  </si>
-  <si>
     <t>T10</t>
   </si>
   <si>
-    <t>Tạo index cho bảng lớn</t>
-  </si>
-  <si>
     <t>T11</t>
   </si>
   <si>
-    <t>Xử lý missing values bằng SQL</t>
-  </si>
-  <si>
-    <t>Ngày 4</t>
-  </si>
-  <si>
     <t>T12</t>
   </si>
   <si>
-    <t>Xử lý duplicate &amp; logic data</t>
-  </si>
-  <si>
     <t>T13</t>
   </si>
   <si>
-    <t>Join 3-5 bảng trong PostgreSQL</t>
-  </si>
-  <si>
-    <t>Ngày 5</t>
-  </si>
-  <si>
     <t>T14</t>
   </si>
   <si>
-    <t>Tối ưu query &amp; kiểm tra performance</t>
-  </si>
-  <si>
     <t>T15</t>
   </si>
   <si>
-    <t>Review &amp; Demo pipeline Data Engineering</t>
-  </si>
-  <si>
-    <t>Ngày 6</t>
-  </si>
-  <si>
     <t>T16</t>
   </si>
   <si>
-    <t>Load data từ PostgreSQL vào Python</t>
-  </si>
-  <si>
-    <t>G2</t>
-  </si>
-  <si>
-    <t>Ngày 7</t>
-  </si>
-  <si>
-    <t>Data Analyst</t>
-  </si>
-  <si>
     <t>T17</t>
   </si>
   <si>
-    <t>EDA cơ bản (thống kê, distribution)</t>
-  </si>
-  <si>
     <t>T18</t>
   </si>
   <si>
-    <t>Phát hiện outliers &amp; correlation</t>
-  </si>
-  <si>
     <t>T19</t>
   </si>
   <si>
-    <t>Tạo ≥10 biến phái sinh (date, promo, competition...)</t>
-  </si>
-  <si>
-    <t>Ngày 8</t>
-  </si>
-  <si>
     <t>T20</t>
   </si>
   <si>
-    <t>Feature selection &amp; document lý do</t>
-  </si>
-  <si>
     <t>T21</t>
   </si>
   <si>
-    <t>Xây dựng visualization nâng cao (heatmap, boxplot)</t>
-  </si>
-  <si>
-    <t>Ngày 9</t>
-  </si>
-  <si>
     <t>T22</t>
   </si>
   <si>
-    <t>Xây dựng interactive dashboard (Streamlit/Plotly)</t>
-  </si>
-  <si>
     <t>T23</t>
   </si>
   <si>
-    <t>Review Feature Engineering &amp; Insights</t>
-  </si>
-  <si>
-    <t>Ngày 10</t>
-  </si>
-  <si>
     <t>T24</t>
   </si>
   <si>
-    <t>Xác định loại bài toán (Regression)</t>
-  </si>
-  <si>
-    <t>Ngày 11</t>
-  </si>
-  <si>
-    <t>ML Engineer</t>
-  </si>
-  <si>
     <t>T25</t>
   </si>
   <si>
-    <t>Train baseline model (XGBoost/RandomForest)</t>
-  </si>
-  <si>
     <t>T26</t>
   </si>
   <si>
-    <t>Đánh giá model (RMSE, MAE...)</t>
-  </si>
-  <si>
-    <t>Ngày 12</t>
-  </si>
-  <si>
     <t>T27</t>
   </si>
   <si>
-    <t>Tuning hyperparameters &amp; Cross-validation</t>
-  </si>
-  <si>
     <t>T28</t>
   </si>
   <si>
-    <t>Thiết kế UI/UX cho Web App</t>
-  </si>
-  <si>
-    <t>Ngày 13</t>
-  </si>
-  <si>
-    <t>Fullstack</t>
-  </si>
-  <si>
     <t>T29</t>
   </si>
   <si>
-    <t>Xây dựng API (Flask/FastAPI)</t>
-  </si>
-  <si>
     <t>T30</t>
   </si>
   <si>
-    <t>Tích hợp model vào backend</t>
-  </si>
-  <si>
-    <t>Ngày 14</t>
-  </si>
-  <si>
     <t>T31</t>
   </si>
   <si>
-    <t>Build frontend &amp; test end-to-end</t>
-  </si>
-  <si>
     <t>T32</t>
   </si>
   <si>
-    <t>Hoàn thiện dashboard tương tác</t>
-  </si>
-  <si>
-    <t>Ngày 15</t>
-  </si>
-  <si>
     <t>T33</t>
   </si>
   <si>
-    <t>Viết hướng dẫn sử dụng &amp; README</t>
-  </si>
-  <si>
     <t>T34</t>
   </si>
   <si>
-    <t>Chuẩn bị slide trình bày</t>
-  </si>
-  <si>
     <t>T35</t>
   </si>
   <si>
-    <t>Demo hệ thống &amp; nhận feedback</t>
-  </si>
-  <si>
-    <t>Ngày 16</t>
-  </si>
-  <si>
     <t>T36</t>
   </si>
   <si>
-    <t>Fix bug theo feedback</t>
-  </si>
-  <si>
-    <t>Ngày 17</t>
-  </si>
-  <si>
     <t>T37</t>
   </si>
   <si>
-    <t>Hoàn thiện báo cáo Word &amp; Code</t>
-  </si>
-  <si>
     <t>T38</t>
   </si>
   <si>
-    <t>Kiểm tra toàn bộ pipeline chạy lại</t>
-  </si>
-  <si>
     <t>T39</t>
   </si>
   <si>
-    <t>Chuẩn bị file nộp (.zip)</t>
-  </si>
-  <si>
-    <t>Review cuối &amp; nộp bài</t>
-  </si>
-  <si>
     <t>Thành viên</t>
   </si>
   <si>
-    <t>Nguyễn Văn Long</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Lóng</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Lòng</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Lọng</t>
-  </si>
-  <si>
     <t>Not Started - Chưa bắt đầu</t>
   </si>
   <si>
@@ -471,58 +252,22 @@
     <t xml:space="preserve">Review - Đang review </t>
   </si>
   <si>
-    <t>Tuần 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hoàn thành Kickoff, phân vai trò, thiết kế schema PostgreSQL, import data</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gặp khó khăn khi join bảng lớn, query chậm</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tuần sau tập trung cleaning &amp; join đầy đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nguyễn Văn Long</t>
-  </si>
-  <si>
-    <t>Tuần 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hoàn thành EDA, tạo 12 biến phái sinh, dashboard prototype</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Feature engineering mất nhiều thời gian hơn dự kiến</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tuần sau train model &amp; tuning</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nguyễn Văn Lòng</t>
-  </si>
-  <si>
-    <t>Tuần 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hoàn thành model, web app, báo cáo</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Lỗi tích hợp model vào web</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fix bug cuối &amp; nộp bài</t>
-  </si>
-  <si>
     <t>Chưa hoàn thành</t>
+  </si>
+  <si>
+    <t>PS47270 Nguyễn Thành Hưng</t>
+  </si>
+  <si>
+    <t>PS48224 Nguyễn Bá Gia Huy</t>
+  </si>
+  <si>
+    <t>PS48172 Phạm Đức Thắng</t>
+  </si>
+  <si>
+    <t>PS48165 Đặng Trịnh Qui Anh</t>
+  </si>
+  <si>
+    <t>PS47694 Đỗ Trọng Thái</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +800,7 @@
         <v>7</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20.7" customHeight="1" x14ac:dyDescent="0.3">
@@ -1069,7 +814,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20.7" customHeight="1" x14ac:dyDescent="0.3">
@@ -1083,7 +828,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="20.7" customHeight="1" x14ac:dyDescent="0.3">
@@ -1189,1002 +934,520 @@
       <c r="A2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="G2" s="22">
-        <v>478834</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>142</v>
-      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H3" s="9"/>
       <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H4" s="9"/>
       <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H5" s="9"/>
       <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H6" s="9"/>
       <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H7" s="9"/>
       <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="H8" s="9"/>
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H9" s="9"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H10" s="9"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="H11" s="9"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H12" s="9"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H13" s="9"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H14" s="9"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="H15" s="9"/>
       <c r="I15" s="14"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H16" s="9"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="9"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="11" t="s">
-        <v>25</v>
-      </c>
+      <c r="H18" s="11"/>
       <c r="I18" s="15"/>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="9"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="11" t="s">
-        <v>52</v>
-      </c>
+      <c r="H19" s="11"/>
       <c r="I19" s="15"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="11"/>
-      <c r="H20" s="11" t="s">
-        <v>25</v>
-      </c>
+      <c r="H20" s="11"/>
       <c r="I20" s="15"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="11"/>
-      <c r="H21" s="11" t="s">
-        <v>25</v>
-      </c>
+      <c r="H21" s="11"/>
       <c r="I21" s="15"/>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="9"/>
       <c r="G22" s="11"/>
-      <c r="H22" s="11" t="s">
-        <v>25</v>
-      </c>
+      <c r="H22" s="11"/>
       <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="9"/>
       <c r="G23" s="11"/>
-      <c r="H23" s="11" t="s">
-        <v>25</v>
-      </c>
+      <c r="H23" s="11"/>
       <c r="I23" s="15"/>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="9"/>
       <c r="G24" s="11"/>
-      <c r="H24" s="11" t="s">
-        <v>25</v>
-      </c>
+      <c r="H24" s="11"/>
       <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H25" s="9"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
       <c r="G26" s="9"/>
-      <c r="H26" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H26" s="9"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H27" s="9"/>
       <c r="I27" s="14"/>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="H28" s="9"/>
       <c r="I28" s="14"/>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="H29" s="9"/>
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H30" s="9"/>
       <c r="I30" s="14"/>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H31" s="9"/>
       <c r="I31" s="14"/>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H32" s="9"/>
       <c r="I32" s="14"/>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="H33" s="9"/>
       <c r="I33" s="14"/>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="H34" s="9"/>
       <c r="I34" s="14"/>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="H35" s="9"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
       <c r="G36" s="9"/>
-      <c r="H36" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H36" s="9"/>
       <c r="I36" s="14"/>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H37" s="9"/>
       <c r="I37" s="14"/>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
       <c r="G38" s="9"/>
-      <c r="H38" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H38" s="9"/>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
       <c r="G39" s="9"/>
-      <c r="H39" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H39" s="9"/>
       <c r="I39" s="14"/>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
       <c r="G40" s="9"/>
-      <c r="H40" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H40" s="9"/>
       <c r="I40" s="14"/>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
       <c r="G41" s="9"/>
-      <c r="H41" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="H41" s="9"/>
       <c r="I41" s="14"/>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2876,7 +2139,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -2887,83 +2150,47 @@
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>152</v>
-      </c>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
     </row>
     <row r="5" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>158</v>
-      </c>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
     </row>
     <row r="6" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>152</v>
-      </c>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
     </row>
     <row r="7" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23"/>
@@ -3100,31 +2327,33 @@
   <sheetData>
     <row r="11" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A16" s="19" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
@@ -3145,27 +2374,27 @@
     </row>
     <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="18" x14ac:dyDescent="0.35">

--- a/Task_Tracker.xlsx
+++ b/Task_Tracker.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>Ngày 7-10</t>
+          <t>09/07 - 12/07/2026</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Ngày 7-10</t>
+          <t>09/07 - 12/07/2026</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Ngày 7-10</t>
+          <t>09/07 - 12/07/2026</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Ngày 11-18</t>
+          <t>13/07 - 20/07/2026</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Ngày 1-6</t>
+          <t>03/07 - 08/07/2026</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
